--- a/Docs/KNOWLEDGE_BASE/REGISTRY/RESEARCH_GAP_REGISTER.xlsx
+++ b/Docs/KNOWLEDGE_BASE/REGISTRY/RESEARCH_GAP_REGISTER.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rea86723a2ac0483c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="2" r:id="Rc208cbbcacb54d40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R4a8e2e3628b2463c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="2" r:id="R53332742e4a443b5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -570,8 +570,7 @@
         <x:v>记录数</x:v>
       </x:c>
       <x:c r="B2" s="7" t="n">
-        <x:f>COUNTA(A4:A5)</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -623,6 +622,23 @@
       </x:c>
       <x:c r="E5" t="str">
         <x:v>追加V72智能决策、Arena、模型和后续缺口记录；既有行保持不变。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>RESEARCH_GAP_REGISTER.xlsx</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>LUOYANG-184-T4-LIVING-WORLD-COMPLETION-MASTER-V1</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>追加洛阳T4 Phase 0—19正式状态、完成证据与Deferred边界；既有行保持不变。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -631,7 +647,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b1cb0591c1e4c21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde56146898164e6d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -679,8 +695,7 @@
         <x:v>记录数</x:v>
       </x:c>
       <x:c r="B2" s="7" t="n">
-        <x:f>COUNTA(A4:A43)</x:f>
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -2267,13 +2282,163 @@
       <x:c r="O43" s="56"/>
       <x:c r="P43" s="56"/>
     </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>RES-GAP-LUOYANG-T4-001</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>GovernmentTax</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>东汉洛阳实物税、免役与减免参数缺少正式校准</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>MEDIUM</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>真实纳税主体、货币/实物转移与政府官仓已实现</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>后汉书|汉简研究|东汉赋役制度研究</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>不得用商业游戏数值替代史料参数</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>建立可追溯税制参数包并用区间校准</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>各税种与身份的适用区间是什么？</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>可引用税率、减免与例外案例</x:v>
+      </x:c>
+      <x:c r="K44" t="str">
+        <x:v>Does not block T4 V1</x:v>
+      </x:c>
+      <x:c r="L44" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="M44" t="str">
+        <x:v>Research changes content parameters, not ledger authority</x:v>
+      </x:c>
+      <x:c r="N44"/>
+      <x:c r="O44" t="str">
+        <x:v>MEDIUM</x:v>
+      </x:c>
+      <x:c r="P44" t="str">
+        <x:v>HAN-LUOYANG-TAX-RESEARCH-V1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>research.map-presentation.han-architecture.v1</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>MapPresentation</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Historically grounded regional Han architecture variants and A-Tier Luoyang compositions</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>Docs/HISTORICAL_WORLD_REFERENCE/LUOYANG_PLAYABLE_VERTICAL_SLICE_MAP_PRESENTATION_AND_CONSTRUCTION_ASSET_LIBRARY_V1/LUOYANG_PLAYABLE_VERTICAL_SLICE_MAP_PRESENTATION_AND_CONSTRUCTION_ASSET_LIBRARY_V1_REPORT.md</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>Archaeological reports and compatible visual references</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>Commercial game art as historical evidence</x:v>
+      </x:c>
+      <x:c r="H45" t="str"/>
+      <x:c r="I45" t="str"/>
+      <x:c r="J45" t="str"/>
+      <x:c r="K45" t="str"/>
+      <x:c r="L45" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="M45" t="str"/>
+      <x:c r="N45" t="str"/>
+      <x:c r="O45" t="str"/>
+      <x:c r="P45" t="str"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>research.global-spatial.han-river-course.v1</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>GlobalSpatialFoundation</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>Han-period local river courses and changed channels remain less certain than modern physical reference.</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>Natural Earth modern generalized rivers + project historical references</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>Historical geography|archaeology|palaeohydrology</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>Modern river geometry as exact Han-period fact</x:v>
+      </x:c>
+      <x:c r="H46" t="str"/>
+      <x:c r="I46" t="str"/>
+      <x:c r="J46" t="str"/>
+      <x:c r="K46" t="str"/>
+      <x:c r="L46" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="M46" t="str"/>
+      <x:c r="N46" t="str"/>
+      <x:c r="O46" t="str"/>
+      <x:c r="P46" t="str"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>research.global-spatial.han-road-corridor.v1</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>GlobalSpatialFoundation</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Detailed Han road widths, alignments, ferries and seasonal passability require regional evidence.</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>R001-R018 modeled strategic corridors</x:v>
+      </x:c>
+      <x:c r="F47" t="str">
+        <x:v>Historical texts|archaeology|regional transport studies</x:v>
+      </x:c>
+      <x:c r="G47" t="str">
+        <x:v>Modeled route Cell path as excavated road geometry</x:v>
+      </x:c>
+      <x:c r="H47" t="str"/>
+      <x:c r="I47" t="str"/>
+      <x:c r="J47" t="str"/>
+      <x:c r="K47" t="str"/>
+      <x:c r="L47" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="M47" t="str"/>
+      <x:c r="N47" t="str"/>
+      <x:c r="O47" t="str"/>
+      <x:c r="P47" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:L1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9916c9beee9d4eef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa8095878b7748e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>